--- a/data/trans_camb/P6901-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 13,42</t>
+          <t>-27,62; 16,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 3,49</t>
+          <t>-33,49; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 14,35</t>
+          <t>-34,82; 16,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 30,24</t>
+          <t>-18,56; 30,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 20,97</t>
+          <t>-22,99; 21,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 25,28</t>
+          <t>-27,66; 25,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 13,86</t>
+          <t>-14,38; 17,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 5,03</t>
+          <t>-22,76; 6,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 11,72</t>
+          <t>-26,8; 13,64</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 20,6</t>
+          <t>-33,36; 24,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 5,12</t>
+          <t>-41,5; 9,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 21,83</t>
+          <t>-41,96; 25,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 52,57</t>
+          <t>-22,42; 53,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 37,17</t>
+          <t>-27,98; 36,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 40,6</t>
+          <t>-33,48; 42,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 21,13</t>
+          <t>-18,13; 26,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 7,57</t>
+          <t>-29,14; 10,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 17,49</t>
+          <t>-35,09; 20,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 19,0</t>
+          <t>-4,87; 21,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 20,51</t>
+          <t>-1,23; 21,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 15,73</t>
+          <t>-15,42; 16,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 9,25</t>
+          <t>-27,26; 10,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 16,26</t>
+          <t>-12,18; 17,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 17,81</t>
+          <t>-12,24; 16,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 13,17</t>
+          <t>-9,1; 12,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 17,41</t>
+          <t>-1,74; 16,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 13,05</t>
+          <t>-8,51; 12,63</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 25,84</t>
+          <t>-5,42; 29,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 28,28</t>
+          <t>-1,17; 29,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 21,6</t>
+          <t>-17,59; 23,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 11,22</t>
+          <t>-29,72; 12,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 20,66</t>
+          <t>-12,75; 22,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 23,47</t>
+          <t>-12,88; 20,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 16,62</t>
+          <t>-10,25; 16,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 22,63</t>
+          <t>-1,74; 21,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 16,78</t>
+          <t>-9,71; 16,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 28,37</t>
+          <t>-8,44; 27,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 23,29</t>
+          <t>-16,61; 24,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,09; -1,54</t>
+          <t>-40,2; -2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 38,19</t>
+          <t>-18,63; 34,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 42,0</t>
+          <t>-14,65; 39,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 23,93</t>
+          <t>-21,35; 24,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 23,13</t>
+          <t>-5,01; 24,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 23,72</t>
+          <t>-7,28; 24,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 2,51</t>
+          <t>-26,56; 1,55</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 43,08</t>
+          <t>-9,39; 40,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 34,35</t>
+          <t>-18,51; 37,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,35; -2,32</t>
+          <t>-48,09; -4,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 76,98</t>
+          <t>-24,04; 60,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 82,88</t>
+          <t>-17,78; 68,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 43,72</t>
+          <t>-25,05; 51,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 36,19</t>
+          <t>-5,94; 37,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 36,15</t>
+          <t>-8,96; 36,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 3,5</t>
+          <t>-32,21; 2,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 27,39</t>
+          <t>-2,55; 30,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 25,93</t>
+          <t>-9,37; 25,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 16,29</t>
+          <t>-26,27; 15,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 23,7</t>
+          <t>-22,82; 24,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 31,28</t>
+          <t>-12,7; 30,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 34,2</t>
+          <t>-11,3; 35,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 22,21</t>
+          <t>-4,96; 21,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 22,06</t>
+          <t>-3,57; 22,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 24,37</t>
+          <t>-9,47; 23,47</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 44,11</t>
+          <t>-2,96; 50,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 40,91</t>
+          <t>-11,64; 42,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 25,41</t>
+          <t>-33,44; 23,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 40,09</t>
+          <t>-27,25; 40,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 51,33</t>
+          <t>-14,8; 51,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 61,77</t>
+          <t>-13,56; 70,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 34,34</t>
+          <t>-5,83; 32,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 34,42</t>
+          <t>-4,61; 34,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 37,56</t>
+          <t>-12,46; 36,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 32,36</t>
+          <t>-25,95; 33,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 38,62</t>
+          <t>-17,3; 39,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 39,55</t>
+          <t>-6,46; 40,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 51,32</t>
+          <t>-26,0; 58,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 56,81</t>
+          <t>-33,93; 55,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 56,98</t>
+          <t>-18,79; 54,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 33,62</t>
+          <t>-14,47; 31,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 37,07</t>
+          <t>-10,37; 35,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 34,48</t>
+          <t>-4,49; 34,18</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 57,88</t>
+          <t>-32,13; 60,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 71,75</t>
+          <t>-19,36; 77,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 81,23</t>
+          <t>-6,87; 88,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 135,26</t>
+          <t>-26,95; 201,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 197,22</t>
+          <t>-32,13; 136,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 210,52</t>
+          <t>-19,6; 170,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 61,24</t>
+          <t>-17,88; 55,07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 66,04</t>
+          <t>-12,47; 64,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 65,08</t>
+          <t>-5,59; 64,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 17,5</t>
+          <t>-19,65; 16,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-52,46; -0,94</t>
+          <t>-52,17; -2,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 11,12</t>
+          <t>-27,99; 12,02</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 41,04</t>
+          <t>-15,93; 39,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,27; 52,92</t>
+          <t>7,35; 53,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 27,69</t>
+          <t>-24,78; 28,58</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 17,88</t>
+          <t>-12,68; 18,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 6,29</t>
+          <t>-34,37; 7,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 9,62</t>
+          <t>-19,08; 9,85</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 26,47</t>
+          <t>-23,31; 25,72</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-63,21; 0,22</t>
+          <t>-66,32; -3,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 16,26</t>
+          <t>-35,54; 18,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 84,76</t>
+          <t>-18,03; 73,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,83; 112,41</t>
+          <t>7,93; 115,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 54,57</t>
+          <t>-27,43; 56,69</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 27,06</t>
+          <t>-15,12; 27,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,9; 9,48</t>
+          <t>-42,29; 10,87</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 13,9</t>
+          <t>-23,06; 14,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-38,15; -2,51</t>
+          <t>-35,29; -1,82</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,11; 27,78</t>
+          <t>1,72; 29,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 15,54</t>
+          <t>-16,04; 14,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 4,13</t>
+          <t>-33,12; 2,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 20,22</t>
+          <t>-6,06; 19,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 3,37</t>
+          <t>-24,94; 4,57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-27,87; -1,79</t>
+          <t>-26,76; -2,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,64; 23,31</t>
+          <t>2,67; 23,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 10,14</t>
+          <t>-12,86; 9,4</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,96; -4,08</t>
+          <t>-49,23; -3,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,16; 46,7</t>
+          <t>2,44; 49,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 25,86</t>
+          <t>-22,16; 24,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 4,74</t>
+          <t>-36,56; 2,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 27,16</t>
+          <t>-6,47; 26,53</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 4,42</t>
+          <t>-27,43; 5,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-36,31; -2,62</t>
+          <t>-35,05; -3,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,26; 34,99</t>
+          <t>3,86; 35,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 15,12</t>
+          <t>-16,6; 13,76</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 7,09</t>
+          <t>-24,29; 7,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-48,57; -12,34</t>
+          <t>-49,15; -12,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,25; 22,82</t>
+          <t>1,06; 22,47</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 23,82</t>
+          <t>-12,59; 26,4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 25,4</t>
+          <t>-19,38; 25,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 15,0</t>
+          <t>-25,72; 15,48</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 9,46</t>
+          <t>-13,97; 10,63</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-31,85; -2,93</t>
+          <t>-31,26; -2,66</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 14,86</t>
+          <t>-10,68; 14,14</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 9,22</t>
+          <t>-30,02; 9,16</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-59,28; -16,3</t>
+          <t>-61,05; -16,6</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,77; 32,2</t>
+          <t>1,81; 31,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 34,81</t>
+          <t>-15,68; 39,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 38,63</t>
+          <t>-23,24; 38,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 20,72</t>
+          <t>-31,17; 22,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 12,49</t>
+          <t>-17,02; 14,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,54; -4,05</t>
+          <t>-39,52; -3,59</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 20,3</t>
+          <t>-12,63; 19,29</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,26</t>
+          <t>-6,76; 5,66</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,86</t>
+          <t>-6,64; 5,08</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 3,93</t>
+          <t>-8,88; 3,84</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 8,13</t>
+          <t>-7,69; 7,15</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 14,08</t>
+          <t>-0,84; 14,08</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 8,01</t>
+          <t>-7,43; 8,84</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,71</t>
+          <t>-5,57; 4,38</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,34</t>
+          <t>-2,14; 7,26</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 5,43</t>
+          <t>-5,19; 4,5</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 7,15</t>
+          <t>-8,69; 7,84</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,13</t>
+          <t>-8,56; 7,08</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 5,39</t>
+          <t>-11,83; 5,18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 10,99</t>
+          <t>-9,46; 9,64</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 19,53</t>
+          <t>-0,96; 19,26</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 10,79</t>
+          <t>-9,13; 12,14</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 6,4</t>
+          <t>-7,0; 5,99</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 9,93</t>
+          <t>-2,75; 9,87</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 7,37</t>
+          <t>-6,72; 5,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6901-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-9,37</t>
+          <t>-4,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-2,6</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 16,56</t>
+          <t>-27,4; 16,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 5,9</t>
+          <t>-32,74; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 16,31</t>
+          <t>-26,64; 15,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 30,74</t>
+          <t>-18,99; 28,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 21,35</t>
+          <t>-22,65; 22,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 25,25</t>
+          <t>-26,67; 23,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 17,01</t>
+          <t>-17,57; 15,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 6,96</t>
+          <t>-24,89; 5,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 13,64</t>
+          <t>-19,53; 14,02</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-12,7%</t>
+          <t>-5,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>-0,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-7,73%</t>
+          <t>-3,56%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 24,91</t>
+          <t>-33,93; 25,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,5; 9,29</t>
+          <t>-41,57; 10,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 25,93</t>
+          <t>-33,18; 26,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 53,6</t>
+          <t>-22,05; 50,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 36,7</t>
+          <t>-28,47; 42,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 42,99</t>
+          <t>-33,06; 38,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 26,18</t>
+          <t>-22,05; 24,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 10,98</t>
+          <t>-30,88; 8,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 20,03</t>
+          <t>-24,73; 21,98</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 21,63</t>
+          <t>-5,09; 20,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 21,01</t>
+          <t>-1,54; 21,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 16,87</t>
+          <t>-13,67; 16,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 10,09</t>
+          <t>-27,99; 7,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 17,46</t>
+          <t>-13,05; 16,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 16,09</t>
+          <t>-11,95; 17,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 12,76</t>
+          <t>-8,66; 11,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 16,3</t>
+          <t>-1,85; 16,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 12,63</t>
+          <t>-9,0; 12,56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 29,82</t>
+          <t>-5,56; 28,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 29,51</t>
+          <t>-1,54; 29,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 23,16</t>
+          <t>-15,76; 22,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 12,41</t>
+          <t>-30,63; 8,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 22,51</t>
+          <t>-13,62; 22,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 20,8</t>
+          <t>-12,75; 22,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 16,25</t>
+          <t>-9,86; 15,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 21,57</t>
+          <t>-2,18; 21,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 16,35</t>
+          <t>-10,19; 16,28</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-22,5</t>
+          <t>-21,74</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 27,52</t>
+          <t>-7,82; 26,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 24,13</t>
+          <t>-17,71; 21,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,2; -2,84</t>
+          <t>-40,75; -3,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 34,05</t>
+          <t>-20,8; 34,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 39,68</t>
+          <t>-16,3; 40,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 24,72</t>
+          <t>-20,54; 24,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 24,72</t>
+          <t>-7,43; 24,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 24,26</t>
+          <t>-9,77; 23,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 1,55</t>
+          <t>-27,66; 2,64</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-28,58%</t>
+          <t>-27,61%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>-0,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 40,65</t>
+          <t>-8,09; 38,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 37,25</t>
+          <t>-20,01; 31,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,09; -4,86</t>
+          <t>-47,56; -6,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 60,33</t>
+          <t>-24,33; 69,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 68,67</t>
+          <t>-19,34; 79,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 51,12</t>
+          <t>-24,34; 50,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 37,68</t>
+          <t>-8,38; 38,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 36,46</t>
+          <t>-11,64; 35,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,21; 2,39</t>
+          <t>-33,08; 3,81</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 30,37</t>
+          <t>-3,87; 28,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 25,67</t>
+          <t>-10,19; 25,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 15,89</t>
+          <t>-23,12; 19,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 24,46</t>
+          <t>-21,59; 24,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 30,37</t>
+          <t>-11,28; 31,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 35,52</t>
+          <t>-17,71; 21,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 21,01</t>
+          <t>-3,86; 22,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 22,93</t>
+          <t>-4,7; 23,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 23,47</t>
+          <t>-13,14; 13,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,54%</t>
+          <t>-1,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>-1,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>-0,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 50,55</t>
+          <t>-3,94; 46,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 42,42</t>
+          <t>-13,15; 40,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 23,95</t>
+          <t>-28,99; 30,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 40,54</t>
+          <t>-25,38; 40,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 51,1</t>
+          <t>-12,59; 54,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 70,08</t>
+          <t>-20,53; 38,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 32,92</t>
+          <t>-4,75; 34,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 34,77</t>
+          <t>-5,64; 36,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 36,18</t>
+          <t>-16,23; 19,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,37</t>
+          <t>16,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,35</t>
+          <t>13,23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,93</t>
+          <t>15,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 33,13</t>
+          <t>-27,03; 32,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 39,9</t>
+          <t>-18,89; 40,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 40,99</t>
+          <t>-6,25; 38,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 58,17</t>
+          <t>-25,9; 56,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 55,44</t>
+          <t>-32,24; 56,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 54,15</t>
+          <t>-18,59; 51,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 31,35</t>
+          <t>-13,58; 32,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 35,69</t>
+          <t>-12,25; 36,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 34,18</t>
+          <t>-2,44; 38,47</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 60,87</t>
+          <t>-34,57; 63,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 77,45</t>
+          <t>-22,24; 77,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 88,87</t>
+          <t>-6,74; 78,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 201,1</t>
+          <t>-29,1; 173,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 136,24</t>
+          <t>-29,55; 194,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 170,71</t>
+          <t>-18,88; 170,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 55,07</t>
+          <t>-16,21; 59,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 64,38</t>
+          <t>-14,08; 69,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 64,67</t>
+          <t>-2,96; 74,3</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-8,26</t>
+          <t>-6,4</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,2</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-4,14</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 16,9</t>
+          <t>-23,01; 16,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-52,17; -2,44</t>
+          <t>-50,13; 0,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 12,02</t>
+          <t>-26,63; 13,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 39,92</t>
+          <t>-16,25; 40,48</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,35; 53,55</t>
+          <t>0,0; 53,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 28,58</t>
+          <t>-24,72; 27,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 18,39</t>
+          <t>-13,62; 16,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 7,07</t>
+          <t>-37,34; 6,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 9,85</t>
+          <t>-17,16; 11,08</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-10,89%</t>
+          <t>-8,43%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-2,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-6,75%</t>
+          <t>-5,45%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 25,72</t>
+          <t>-26,54; 23,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,32; -3,9</t>
+          <t>-61,48; 0,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 18,12</t>
+          <t>-32,7; 21,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 73,77</t>
+          <t>-18,17; 76,66</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,93; 115,27</t>
+          <t>0,0; 115,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 56,69</t>
+          <t>-27,0; 51,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 27,75</t>
+          <t>-16,67; 24,58</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 10,87</t>
+          <t>-46,62; 8,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 14,59</t>
+          <t>-20,66; 16,77</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-10,11</t>
+          <t>-7,91</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-35,29; -1,82</t>
+          <t>-34,47; 1,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,72; 29,6</t>
+          <t>1,01; 29,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 14,9</t>
+          <t>-13,14; 17,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 2,14</t>
+          <t>-31,09; 4,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 19,94</t>
+          <t>-6,25; 20,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 4,57</t>
+          <t>-20,58; 6,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-26,76; -2,55</t>
+          <t>-27,19; -1,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,67; 23,09</t>
+          <t>2,21; 23,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 9,4</t>
+          <t>-9,65; 11,26</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-11,94%</t>
+          <t>-9,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,82%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,23; -3,53</t>
+          <t>-48,84; 0,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2,44; 49,93</t>
+          <t>1,67; 50,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 24,72</t>
+          <t>-17,7; 27,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 2,31</t>
+          <t>-35,3; 5,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 26,53</t>
+          <t>-6,75; 27,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 5,43</t>
+          <t>-23,25; 8,89</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,05; -3,85</t>
+          <t>-35,62; -2,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,86; 35,23</t>
+          <t>2,86; 35,05</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 13,76</t>
+          <t>-12,19; 16,17</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12,68</t>
+          <t>13,14</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>9,46</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 7,04</t>
+          <t>-23,93; 6,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-49,15; -12,25</t>
+          <t>-48,34; -12,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,06; 22,47</t>
+          <t>2,57; 22,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 26,4</t>
+          <t>-11,73; 25,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 25,7</t>
+          <t>-18,53; 26,12</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 15,48</t>
+          <t>-9,8; 21,53</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 10,63</t>
+          <t>-13,99; 9,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-31,26; -2,66</t>
+          <t>-31,94; -2,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 14,14</t>
+          <t>0,68; 17,77</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-2,38%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 9,16</t>
+          <t>-29,48; 8,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-61,05; -16,6</t>
+          <t>-59,22; -16,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1,81; 31,28</t>
+          <t>3,19; 30,89</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 39,25</t>
+          <t>-14,09; 38,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 38,13</t>
+          <t>-22,02; 40,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 22,34</t>
+          <t>-11,8; 33,18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 14,33</t>
+          <t>-17,43; 13,07</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -3,59</t>
+          <t>-39,37; -3,26</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 19,29</t>
+          <t>0,57; 24,61</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,66</t>
+          <t>-7,46; 5,7</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,08</t>
+          <t>-6,98; 6,08</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 3,84</t>
+          <t>-6,31; 5,75</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 7,15</t>
+          <t>-8,41; 8,11</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 14,08</t>
+          <t>-1,15; 14,66</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 8,84</t>
+          <t>-7,17; 6,45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,38</t>
+          <t>-5,67; 4,38</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,26</t>
+          <t>-2,77; 7,33</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 4,5</t>
+          <t>-4,46; 4,5</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-3,1%</t>
+          <t>-0,29%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>-0,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-0,74%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 7,84</t>
+          <t>-9,69; 7,73</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,08</t>
+          <t>-8,9; 8,34</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 5,18</t>
+          <t>-8,24; 7,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 9,64</t>
+          <t>-10,44; 10,94</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 19,26</t>
+          <t>-1,39; 20,0</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 12,14</t>
+          <t>-8,59; 8,77</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 5,99</t>
+          <t>-7,1; 5,96</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 9,87</t>
+          <t>-3,54; 9,96</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 5,99</t>
+          <t>-5,66; 6,14</t>
         </is>
       </c>
     </row>
